--- a/artfynd/A 16130-2025 artfynd.xlsx
+++ b/artfynd/A 16130-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>125877868</v>
       </c>
       <c r="B8" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>125877870</v>
       </c>
       <c r="B11" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>125877869</v>
       </c>
       <c r="B14" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 16130-2025 artfynd.xlsx
+++ b/artfynd/A 16130-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125877877</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>125877879</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>125877873</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>125877880</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>125877878</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>125877868</v>
       </c>
       <c r="B8" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>125877871</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>125877876</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>125877870</v>
       </c>
       <c r="B11" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>125877874</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>125877869</v>
       </c>
       <c r="B14" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>125877872</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 16130-2025 artfynd.xlsx
+++ b/artfynd/A 16130-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>125877868</v>
       </c>
       <c r="B8" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>125877870</v>
       </c>
       <c r="B11" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,32 +1758,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125877874</v>
+        <v>125877869</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>98334</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780612</v>
+        <v>780762</v>
       </c>
       <c r="R13" t="n">
-        <v>7228464</v>
+        <v>7228275</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125877869</v>
+        <v>125877874</v>
       </c>
       <c r="B14" t="n">
-        <v>98332</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780762</v>
+        <v>780612</v>
       </c>
       <c r="R14" t="n">
-        <v>7228275</v>
+        <v>7228464</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 16130-2025 artfynd.xlsx
+++ b/artfynd/A 16130-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125877877</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>125877879</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>125877873</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>125877880</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>125877878</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>125877868</v>
       </c>
       <c r="B8" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>125877871</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>125877876</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>125877870</v>
       </c>
       <c r="B11" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,32 +1758,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125877869</v>
+        <v>125877874</v>
       </c>
       <c r="B13" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780762</v>
+        <v>780612</v>
       </c>
       <c r="R13" t="n">
-        <v>7228275</v>
+        <v>7228464</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125877874</v>
+        <v>125877869</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780612</v>
+        <v>780762</v>
       </c>
       <c r="R14" t="n">
-        <v>7228464</v>
+        <v>7228275</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,7 +1955,7 @@
         <v>125877872</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 16130-2025 artfynd.xlsx
+++ b/artfynd/A 16130-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>125877868</v>
       </c>
       <c r="B8" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>125877870</v>
       </c>
       <c r="B11" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>125877869</v>
       </c>
       <c r="B14" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 16130-2025 artfynd.xlsx
+++ b/artfynd/A 16130-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125877877</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125877864</v>
       </c>
       <c r="B3" t="n">
-        <v>57473</v>
+        <v>57474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>125877879</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>125877873</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>125877880</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>125877878</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>125877868</v>
       </c>
       <c r="B8" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>125877871</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>125877876</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>125877870</v>
       </c>
       <c r="B11" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>125877865</v>
       </c>
       <c r="B12" t="n">
-        <v>57473</v>
+        <v>57474</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>125877874</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>125877869</v>
       </c>
       <c r="B14" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>125877872</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 16130-2025 artfynd.xlsx
+++ b/artfynd/A 16130-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>125877868</v>
       </c>
       <c r="B8" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>125877870</v>
       </c>
       <c r="B11" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,32 +1758,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125877874</v>
+        <v>125877869</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780612</v>
+        <v>780762</v>
       </c>
       <c r="R13" t="n">
-        <v>7228464</v>
+        <v>7228275</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125877869</v>
+        <v>125877874</v>
       </c>
       <c r="B14" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780762</v>
+        <v>780612</v>
       </c>
       <c r="R14" t="n">
-        <v>7228275</v>
+        <v>7228464</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 16130-2025 artfynd.xlsx
+++ b/artfynd/A 16130-2025 artfynd.xlsx
@@ -1758,32 +1758,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125877869</v>
+        <v>125877874</v>
       </c>
       <c r="B13" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780762</v>
+        <v>780612</v>
       </c>
       <c r="R13" t="n">
-        <v>7228275</v>
+        <v>7228464</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125877874</v>
+        <v>125877869</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780612</v>
+        <v>780762</v>
       </c>
       <c r="R14" t="n">
-        <v>7228464</v>
+        <v>7228275</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 16130-2025 artfynd.xlsx
+++ b/artfynd/A 16130-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>125877868</v>
       </c>
       <c r="B8" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>125877870</v>
       </c>
       <c r="B11" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>125877869</v>
       </c>
       <c r="B14" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 16130-2025 artfynd.xlsx
+++ b/artfynd/A 16130-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125877877</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125877864</v>
       </c>
       <c r="B3" t="n">
-        <v>57474</v>
+        <v>57478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>125877879</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>125877873</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>125877880</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>125877878</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>125877868</v>
       </c>
       <c r="B8" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>125877871</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>125877876</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>125877870</v>
       </c>
       <c r="B11" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>125877865</v>
       </c>
       <c r="B12" t="n">
-        <v>57474</v>
+        <v>57478</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,32 +1758,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125877874</v>
+        <v>125877869</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>98349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780612</v>
+        <v>780762</v>
       </c>
       <c r="R13" t="n">
-        <v>7228464</v>
+        <v>7228275</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125877869</v>
+        <v>125877874</v>
       </c>
       <c r="B14" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780762</v>
+        <v>780612</v>
       </c>
       <c r="R14" t="n">
-        <v>7228275</v>
+        <v>7228464</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,7 +1955,7 @@
         <v>125877872</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 16130-2025 artfynd.xlsx
+++ b/artfynd/A 16130-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>125877868</v>
       </c>
       <c r="B8" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>125877870</v>
       </c>
       <c r="B11" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>125877869</v>
       </c>
       <c r="B13" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16130-2025 artfynd.xlsx
+++ b/artfynd/A 16130-2025 artfynd.xlsx
@@ -1758,32 +1758,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125877869</v>
+        <v>125877874</v>
       </c>
       <c r="B13" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780762</v>
+        <v>780612</v>
       </c>
       <c r="R13" t="n">
-        <v>7228275</v>
+        <v>7228464</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125877874</v>
+        <v>125877869</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780612</v>
+        <v>780762</v>
       </c>
       <c r="R14" t="n">
-        <v>7228464</v>
+        <v>7228275</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 16130-2025 artfynd.xlsx
+++ b/artfynd/A 16130-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125877877</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125877864</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>125877879</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>125877873</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>125877880</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>125877878</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>125877868</v>
       </c>
       <c r="B8" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>125877871</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>125877876</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>125877870</v>
       </c>
       <c r="B11" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>125877865</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57479</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>125877874</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>125877869</v>
       </c>
       <c r="B14" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>125877872</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 16130-2025 artfynd.xlsx
+++ b/artfynd/A 16130-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125877877</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>125877864</v>
       </c>
       <c r="B3" t="n">
-        <v>57479</v>
+        <v>57483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,14 +877,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>125877879</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,14 +978,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>125877873</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,14 +1079,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>125877880</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,14 +1180,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>125877878</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,14 +1281,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>125877868</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,14 +1382,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>125877871</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,14 +1483,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>125877876</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,14 +1584,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>125877870</v>
       </c>
       <c r="B11" t="n">
-        <v>98361</v>
+        <v>98448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,14 +1685,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>125877865</v>
       </c>
       <c r="B12" t="n">
-        <v>57479</v>
+        <v>57483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,14 +1794,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>125877874</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,14 +1895,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>125877869</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>98448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,14 +1996,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>125877872</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2045,7 +2097,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16130-2025 artfynd.xlsx
+++ b/artfynd/A 16130-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125877877</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>125877864</v>
       </c>
       <c r="B3" t="n">
-        <v>57483</v>
+        <v>57485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>125877879</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>125877873</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>125877880</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>125877878</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>125877868</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>125877871</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>125877876</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>125877870</v>
       </c>
       <c r="B11" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>125877865</v>
       </c>
       <c r="B12" t="n">
-        <v>57483</v>
+        <v>57485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>125877874</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>125877869</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>125877872</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
